--- a/docs/project_implementation.xlsx
+++ b/docs/project_implementation.xlsx
@@ -4,20 +4,22 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="20055" windowHeight="7695" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="135" windowWidth="20055" windowHeight="7695"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="core_functionality" sheetId="2" r:id="rId2"/>
+    <sheet name="Issue" sheetId="1" r:id="rId1"/>
+    <sheet name="new_functionality" sheetId="2" r:id="rId2"/>
     <sheet name="interview" sheetId="3" r:id="rId3"/>
     <sheet name="noteboo" sheetId="4" r:id="rId4"/>
+    <sheet name="todo" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
   <si>
     <t>Need to generate the architecture of application</t>
   </si>
@@ -40,14 +42,7 @@
     <t>Nodes.py --&gt; can keep prompts in some other directory ; PENDING</t>
   </si>
   <si>
-    <t>is streamlit production ready, if not what is production ready that 
-we can take and replace the complete codebase in that</t>
-  </si>
-  <si>
     <t>how to manage user authentctio and user session ?</t>
-  </si>
-  <si>
-    <t> Notebook to learn/test checkpointer</t>
   </si>
   <si>
     <t># Which guardrails api is usd in production?</t>
@@ -141,7 +136,195 @@
     <t>STAUS</t>
   </si>
   <si>
-    <t>Refactor notebook based on codechange ?</t>
+    <t>RAG</t>
+  </si>
+  <si>
+    <t>Ingestion Pipeline  ===&gt; shuld be automated using AIRFLOW</t>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>Ingestion Piepline Notebook ==&gt; to Ingest Data functionality testing</t>
+  </si>
+  <si>
+    <t>is streamlit production ready, if not what is production ready that we can take and replace the complete codebase in that</t>
+  </si>
+  <si>
+    <r>
+      <t>02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Guardrails (PII, SQL injection, prompt injection)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Intent Classification (GPT-4o + keyword fallback)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — LiteLLM Fallback Chain</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — LangGraph State &amp; Graph Flow</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Individual Agents (one per agent)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — HITL (Human-in-the-Loop)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — FastAPI endpoints</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — pgvector / RAG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — End-to-end smoke test</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Redis Cache (this one)</t>
+    </r>
+  </si>
+  <si>
+    <t>Agents</t>
+  </si>
+  <si>
+    <t>Capacity Agent ==&gt; Jira Client should be in some utils folder</t>
+  </si>
+  <si>
+    <t>How to document will be ingested in this application ? Where is RAG</t>
+  </si>
+  <si>
+    <t>How TO TEST DAY 17( Teams)</t>
+  </si>
+  <si>
+    <t>How TO TEST DAY 18( MCP)</t>
   </si>
 </sst>
 </file>
@@ -212,7 +395,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -235,11 +418,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -255,6 +449,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,33 +745,176 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:C4"/>
+  <dimension ref="B2:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
-      <c r="C2" t="s">
+    <row r="2" spans="2:6" ht="18.75">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="18.75">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:3">
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3">
-      <c r="B4">
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="18.75">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
+      <c r="C4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="2:6" ht="37.5">
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="2:6" ht="18.75">
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" spans="2:6" ht="30.75">
+      <c r="B7" s="4">
+        <v>5</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="2:6" ht="18.75">
+      <c r="B8" s="4">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="2:6" ht="18.75">
+      <c r="B9" s="4">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="2:6" ht="18.75">
+      <c r="B10" s="4">
+        <v>8</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="2:6" ht="18.75">
+      <c r="B11" s="4">
+        <v>9</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="2:6" ht="18.75">
+      <c r="B12" s="4">
+        <v>10</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="2:6" ht="18.75">
+      <c r="B13" s="4">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="2:6" ht="18.75">
+      <c r="B14" s="4">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -594,16 +933,16 @@
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18.75">
@@ -632,20 +971,16 @@
       <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="B5" s="6"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5" ht="37.5">
+    <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="B6" s="7"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -655,7 +990,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -666,49 +1001,33 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5"/>
-      <c r="B9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5" ht="30.75">
-      <c r="A10" s="4">
-        <v>7</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>34</v>
-      </c>
+    <row r="10" spans="1:5" ht="18.75">
+      <c r="A10" s="4"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="5">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>37</v>
-      </c>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
@@ -746,22 +1065,22 @@
     </row>
     <row r="4" spans="3:3" ht="18.75">
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="3:3" ht="18.75">
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="3:3" ht="18.75">
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="3:3" ht="18.75">
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="3:3">
@@ -769,27 +1088,27 @@
     </row>
     <row r="9" spans="3:3" ht="18.75">
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="3:3" ht="18.75">
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="3:3" ht="18.75">
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="3:3" ht="18.75">
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="3:3" ht="18.75">
       <c r="C13" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="3:3">
@@ -800,7 +1119,7 @@
     </row>
     <row r="16" spans="3:3" ht="18.75">
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="3:3">
@@ -808,17 +1127,17 @@
     </row>
     <row r="18" spans="3:3" ht="18.75">
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="3:3" ht="18.75">
       <c r="C19" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="3:3" ht="18.75">
       <c r="C20" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="3:3">
@@ -826,7 +1145,7 @@
     </row>
     <row r="22" spans="3:3" ht="18.75">
       <c r="C22" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="3:3">
@@ -834,7 +1153,7 @@
     </row>
     <row r="24" spans="3:3" ht="18.75">
       <c r="C24" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="3:3">
@@ -842,7 +1161,7 @@
     </row>
     <row r="26" spans="3:3" ht="18.75">
       <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="3:3">
@@ -850,7 +1169,7 @@
     </row>
     <row r="28" spans="3:3" ht="18.75">
       <c r="C28" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="3:3">
@@ -861,12 +1180,12 @@
     </row>
     <row r="31" spans="3:3" ht="18.75">
       <c r="C31" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="3:3" ht="18.75">
       <c r="C32" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -876,23 +1195,106 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C3:C4"/>
+  <dimension ref="C3:C12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="54.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:3" ht="18.75">
-      <c r="C3" s="1" t="s">
-        <v>9</v>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="3:3">
-      <c r="C4" t="s">
-        <v>40</v>
+      <c r="C4" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="12" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="C2:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="44.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:4">
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="3:4">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4">
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/project_implementation.xlsx
+++ b/docs/project_implementation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
   <si>
     <t>Need to generate the architecture of application</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>How TO TEST DAY 18( MCP)</t>
+  </si>
+  <si>
+    <t>How to do Integration testing --&gt; Complete Functionality Testing</t>
   </si>
 </sst>
 </file>
@@ -745,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:F14"/>
+  <dimension ref="B2:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
@@ -915,6 +918,11 @@
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="C15" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/project_implementation.xlsx
+++ b/docs/project_implementation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="20055" windowHeight="7695"/>
+    <workbookView xWindow="240" yWindow="135" windowWidth="20055" windowHeight="7695" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Issue" sheetId="1" r:id="rId1"/>

--- a/docs/project_implementation.xlsx
+++ b/docs/project_implementation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="20055" windowHeight="7695" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="135" windowWidth="20055" windowHeight="7695"/>
   </bookViews>
   <sheets>
     <sheet name="Issue" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
   <si>
     <t>Need to generate the architecture of application</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>how to manage user authentctio and user session ?</t>
-  </si>
-  <si>
-    <t># Which guardrails api is usd in production?</t>
   </si>
   <si>
     <t>GuardRails</t>
@@ -328,6 +325,15 @@
   </si>
   <si>
     <t>How to do Integration testing --&gt; Complete Functionality Testing</t>
+  </si>
+  <si>
+    <t>LLM Gateway</t>
+  </si>
+  <si>
+    <t>Which guardrails api is usd in production?</t>
+  </si>
+  <si>
+    <t>How to implement the complete project in AWS Agenctic core or  with AWS Service ?</t>
   </si>
 </sst>
 </file>
@@ -748,180 +754,180 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:F15"/>
+  <dimension ref="A2:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="94.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.75">
-      <c r="B2" s="8"/>
-      <c r="C2" s="8" t="s">
-        <v>30</v>
+    <row r="2" spans="1:5" ht="18.75">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="18.75">
-      <c r="B3" s="4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="18.75">
-      <c r="B4" s="4">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18.75">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="2:6" ht="37.5">
-      <c r="B5" s="4">
+    </row>
+    <row r="5" spans="1:5" ht="37.5">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="2:6" ht="18.75">
-      <c r="B6" s="4">
+    </row>
+    <row r="6" spans="1:5" ht="18.75">
+      <c r="A6" s="4">
         <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" ht="30.75">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" ht="18.75">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="2:6" ht="30.75">
-      <c r="B7" s="4">
-        <v>5</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" ht="18.75">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" ht="18.75">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" ht="18.75">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="2:6" ht="18.75">
-      <c r="B8" s="4">
-        <v>6</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="2:6" ht="18.75">
-      <c r="B9" s="4">
-        <v>7</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="2:6" ht="18.75">
-      <c r="B10" s="4">
-        <v>8</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="2:6" ht="18.75">
-      <c r="B11" s="4">
-        <v>9</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" ht="18.75">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="2:6" ht="18.75">
-      <c r="B12" s="4">
-        <v>10</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" ht="18.75">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="2:6" ht="18.75">
-      <c r="B13" s="4">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="2:6" ht="18.75">
-      <c r="B14" s="4">
+    </row>
+    <row r="14" spans="1:5" ht="18.75">
+      <c r="A14" s="4">
         <v>11</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="B14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="C15" s="11" t="s">
-        <v>58</v>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="11" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -934,23 +940,23 @@
   <dimension ref="A2:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="102.85546875" customWidth="1"/>
+    <col min="2" max="2" width="97.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18.75">
@@ -976,10 +982,12 @@
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -988,7 +996,7 @@
       <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="4"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -997,7 +1005,7 @@
       <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="5"/>
@@ -1008,39 +1016,47 @@
       <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>9</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+    <row r="9" spans="1:5" ht="18.75">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" ht="18.75">
-      <c r="A10" s="4"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+    <row r="11" spans="1:5" ht="18.75">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="18.75">
       <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
+      <c r="B12" s="4"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -1073,22 +1089,22 @@
     </row>
     <row r="4" spans="3:3" ht="18.75">
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="3:3" ht="18.75">
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="3:3" ht="18.75">
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="3:3" ht="18.75">
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="3:3">
@@ -1096,27 +1112,27 @@
     </row>
     <row r="9" spans="3:3" ht="18.75">
       <c r="C9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="3:3" ht="18.75">
       <c r="C10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="3:3" ht="18.75">
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="3:3" ht="18.75">
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="3:3" ht="18.75">
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="3:3">
@@ -1127,7 +1143,7 @@
     </row>
     <row r="16" spans="3:3" ht="18.75">
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="3:3">
@@ -1135,17 +1151,17 @@
     </row>
     <row r="18" spans="3:3" ht="18.75">
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="3:3" ht="18.75">
       <c r="C19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="3:3" ht="18.75">
       <c r="C20" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="3:3">
@@ -1153,7 +1169,7 @@
     </row>
     <row r="22" spans="3:3" ht="18.75">
       <c r="C22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="3:3">
@@ -1161,7 +1177,7 @@
     </row>
     <row r="24" spans="3:3" ht="18.75">
       <c r="C24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="3:3">
@@ -1169,7 +1185,7 @@
     </row>
     <row r="26" spans="3:3" ht="18.75">
       <c r="C26" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="3:3">
@@ -1177,7 +1193,7 @@
     </row>
     <row r="28" spans="3:3" ht="18.75">
       <c r="C28" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="3:3">
@@ -1188,12 +1204,12 @@
     </row>
     <row r="31" spans="3:3" ht="18.75">
       <c r="C31" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="3:3" ht="18.75">
       <c r="C32" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1211,52 +1227,52 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
